--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_10.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_10.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.03061792533744025</v>
+        <v>0.02619102054058937</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00846437886825821</v>
+        <v>0.00845820783045732</v>
       </c>
       <c r="C2" t="n">
-        <v>62962770</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>62962770</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>42449975</v>
+        <v>4015507</v>
       </c>
       <c r="L2" t="n">
-        <v>22103097</v>
+        <v>1757272</v>
       </c>
       <c r="M2" t="n">
-        <v>4999343</v>
+        <v>326182</v>
       </c>
       <c r="N2" t="n">
-        <v>190724</v>
+        <v>5126</v>
       </c>
       <c r="O2" t="n">
-        <v>3088312</v>
+        <v>203858</v>
       </c>
       <c r="P2" t="n">
-        <v>1151970</v>
+        <v>44395</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999843239784241</v>
+        <v>0.99997878074646</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8219994306564331</v>
+        <v>0.7337086796760559</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6737678647041321</v>
+        <v>0.5503703355789185</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5945190191268921</v>
+        <v>0.4244762659072876</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2437981218099594</v>
+        <v>0.06564977765083313</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6467819213867188</v>
+        <v>0.4671142399311066</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7749843001365662</v>
+        <v>0.6550543904304504</v>
       </c>
       <c r="X2" t="n">
-        <v>62962770</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>62962770</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>47766368</v>
+        <v>4750163</v>
       </c>
       <c r="AG2" t="n">
-        <v>29788699</v>
+        <v>3018205</v>
       </c>
       <c r="AH2" t="n">
-        <v>8012790</v>
+        <v>806591</v>
       </c>
       <c r="AI2" t="n">
-        <v>590209</v>
+        <v>59281</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4597208</v>
+        <v>461241</v>
       </c>
       <c r="AK2" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9558600783348083</v>
+        <v>0.9546809196472168</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9117661118507385</v>
+        <v>0.9128581881523132</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8583323359489441</v>
+        <v>0.8581860065460205</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618221402168274</v>
+        <v>0.6609027981758118</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020313024520874</v>
+        <v>0.901951789855957</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314513206481934</v>
+        <v>0.9314922094345093</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.008050113388549501</v>
+        <v>0.006753047098569929</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002029700193242254</v>
+        <v>0.002027664927559576</v>
       </c>
       <c r="C3" t="n">
-        <v>451</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>42449975</v>
+        <v>4015507</v>
       </c>
       <c r="E3" t="n">
-        <v>7187885</v>
+        <v>906558</v>
       </c>
       <c r="F3" t="n">
-        <v>212673</v>
+        <v>33697</v>
       </c>
       <c r="G3" t="n">
-        <v>15604</v>
+        <v>1734</v>
       </c>
       <c r="H3" t="n">
-        <v>16250</v>
+        <v>2536</v>
       </c>
       <c r="I3" t="n">
-        <v>637</v>
+        <v>60</v>
       </c>
       <c r="J3" t="n">
-        <v>99900243</v>
+        <v>10016488</v>
       </c>
       <c r="K3" t="n">
-        <v>103788159</v>
+        <v>9912105</v>
       </c>
       <c r="L3" t="n">
-        <v>119418378</v>
+        <v>11574850</v>
       </c>
       <c r="M3" t="n">
-        <v>150107293</v>
+        <v>14945492</v>
       </c>
       <c r="N3" t="n">
-        <v>161379721</v>
+        <v>16166837</v>
       </c>
       <c r="O3" t="n">
-        <v>156077483</v>
+        <v>15585129</v>
       </c>
       <c r="P3" t="n">
-        <v>160594914</v>
+        <v>16112417</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8509827256202698</v>
+        <v>0.8095597624778748</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6750375628471375</v>
+        <v>0.529437243938446</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5348609685897827</v>
+        <v>0.3463183343410492</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2136484831571579</v>
+        <v>0.0570773221552372</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6055585145950317</v>
+        <v>0.3982309401035309</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5954524278640747</v>
+        <v>0.2290704548358917</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>47766368</v>
+        <v>4750163</v>
       </c>
       <c r="Z3" t="n">
-        <v>1964194</v>
+        <v>194702</v>
       </c>
       <c r="AA3" t="n">
-        <v>84460</v>
+        <v>8398</v>
       </c>
       <c r="AB3" t="n">
-        <v>67907</v>
+        <v>6808</v>
       </c>
       <c r="AC3" t="n">
-        <v>246</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>99901230</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>110774760</v>
+        <v>11143996</v>
       </c>
       <c r="AG3" t="n">
-        <v>127237766</v>
+        <v>12722349</v>
       </c>
       <c r="AH3" t="n">
-        <v>152194495</v>
+        <v>15254456</v>
       </c>
       <c r="AI3" t="n">
-        <v>161669715</v>
+        <v>16209376</v>
       </c>
       <c r="AJ3" t="n">
-        <v>157264762</v>
+        <v>15767551</v>
       </c>
       <c r="AK3" t="n">
-        <v>160796809</v>
+        <v>16122526</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575589299201965</v>
+        <v>0.9576725363731384</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.909758985042572</v>
+        <v>0.9093356132507324</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572583794593811</v>
+        <v>0.8563846349716187</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6611504554748535</v>
+        <v>0.6600859761238098</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014239311218262</v>
+        <v>0.9010214805603027</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311903715133667</v>
+        <v>0.9309202432632446</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06909505406176435</v>
+        <v>0.0609667387408707</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03200867295972447</v>
+        <v>0.03198836053224347</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>8476373</v>
+        <v>1316449</v>
       </c>
       <c r="E4" t="n">
-        <v>22103097</v>
+        <v>1757272</v>
       </c>
       <c r="F4" t="n">
-        <v>1831108</v>
+        <v>200402</v>
       </c>
       <c r="G4" t="n">
-        <v>87930</v>
+        <v>10597</v>
       </c>
       <c r="H4" t="n">
-        <v>226377</v>
+        <v>32646</v>
       </c>
       <c r="I4" t="n">
-        <v>18607</v>
+        <v>1761</v>
       </c>
       <c r="J4" t="n">
-        <v>987</v>
+        <v>134</v>
       </c>
       <c r="K4" t="n">
-        <v>9192366</v>
+        <v>1457383</v>
       </c>
       <c r="L4" t="n">
-        <v>10702115</v>
+        <v>1435618</v>
       </c>
       <c r="M4" t="n">
-        <v>3409712</v>
+        <v>442252</v>
       </c>
       <c r="N4" t="n">
-        <v>591579</v>
+        <v>72955</v>
       </c>
       <c r="O4" t="n">
-        <v>1686577</v>
+        <v>232562</v>
       </c>
       <c r="P4" t="n">
-        <v>334473</v>
+        <v>23378</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999921917915344</v>
+        <v>0.99998939037323</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8362399935722351</v>
+        <v>0.7697702050209045</v>
       </c>
       <c r="S4" t="n">
-        <v>0.674402117729187</v>
+        <v>0.5397009253501892</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5631143450737</v>
+        <v>0.3814347386360168</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2277297377586365</v>
+        <v>0.06106416136026382</v>
       </c>
       <c r="V4" t="n">
-        <v>0.625491738319397</v>
+        <v>0.4299309551715851</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6734587550163269</v>
+        <v>0.3394398391246796</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2060120</v>
+        <v>210743</v>
       </c>
       <c r="Z4" t="n">
-        <v>29788699</v>
+        <v>3018205</v>
       </c>
       <c r="AA4" t="n">
-        <v>827465</v>
+        <v>83377</v>
       </c>
       <c r="AB4" t="n">
-        <v>55180</v>
+        <v>5608</v>
       </c>
       <c r="AC4" t="n">
-        <v>11363</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>680</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2205765</v>
+        <v>225492</v>
       </c>
       <c r="AG4" t="n">
-        <v>2882727</v>
+        <v>288119</v>
       </c>
       <c r="AH4" t="n">
-        <v>1322510</v>
+        <v>133288</v>
       </c>
       <c r="AI4" t="n">
-        <v>301585</v>
+        <v>30416</v>
       </c>
       <c r="AJ4" t="n">
-        <v>499298</v>
+        <v>50140</v>
       </c>
       <c r="AK4" t="n">
-        <v>132578</v>
+        <v>13269</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567087888717651</v>
+        <v>0.956174373626709</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9107614159584045</v>
+        <v>0.9110934734344482</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577950596809387</v>
+        <v>0.8572843670845032</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6614861488342285</v>
+        <v>0.6604941487312317</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901727557182312</v>
+        <v>0.9014863967895508</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.93132084608078</v>
+        <v>0.9312061071395874</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>510713</v>
+        <v>104548</v>
       </c>
       <c r="E5" t="n">
-        <v>2828467</v>
+        <v>402505</v>
       </c>
       <c r="F5" t="n">
-        <v>4999343</v>
+        <v>326182</v>
       </c>
       <c r="G5" t="n">
-        <v>197119</v>
+        <v>20176</v>
       </c>
       <c r="H5" t="n">
-        <v>738581</v>
+        <v>81397</v>
       </c>
       <c r="I5" t="n">
-        <v>72687</v>
+        <v>7024</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7433500</v>
+        <v>944605</v>
       </c>
       <c r="L5" t="n">
-        <v>10640410</v>
+        <v>1561860</v>
       </c>
       <c r="M5" t="n">
-        <v>4347652</v>
+        <v>615674</v>
       </c>
       <c r="N5" t="n">
-        <v>701976</v>
+        <v>84682</v>
       </c>
       <c r="O5" t="n">
-        <v>2011628</v>
+        <v>308051</v>
       </c>
       <c r="P5" t="n">
-        <v>782643</v>
+        <v>149410</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999939203262329</v>
+        <v>0.999991774559021</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8979156613349915</v>
+        <v>0.8529058694839478</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8689548969268799</v>
+        <v>0.8164389729499817</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9523690938949585</v>
+        <v>0.9352142214775085</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9920574426651001</v>
+        <v>0.9903465509414673</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9772926568984985</v>
+        <v>0.9668936729431152</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9931408166885376</v>
+        <v>0.9894187450408936</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>80221</v>
+        <v>8120</v>
       </c>
       <c r="Z5" t="n">
-        <v>856225</v>
+        <v>87176</v>
       </c>
       <c r="AA5" t="n">
-        <v>8012790</v>
+        <v>806591</v>
       </c>
       <c r="AB5" t="n">
-        <v>99697</v>
+        <v>10039</v>
       </c>
       <c r="AC5" t="n">
-        <v>291732</v>
+        <v>29297</v>
       </c>
       <c r="AD5" t="n">
-        <v>6330</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2117107</v>
+        <v>209949</v>
       </c>
       <c r="AG5" t="n">
-        <v>2954808</v>
+        <v>300927</v>
       </c>
       <c r="AH5" t="n">
-        <v>1334205</v>
+        <v>135265</v>
       </c>
       <c r="AI5" t="n">
-        <v>302491</v>
+        <v>30527</v>
       </c>
       <c r="AJ5" t="n">
-        <v>502732</v>
+        <v>50668</v>
       </c>
       <c r="AK5" t="n">
-        <v>133120</v>
+        <v>13388</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734571576118469</v>
+        <v>0.9733342528343201</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641569852828979</v>
+        <v>0.963927686214447</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836875200271606</v>
+        <v>0.9835542440414429</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996290922164917</v>
+        <v>0.9962679147720337</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938474297523499</v>
+        <v>0.993826687335968</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983685612678528</v>
+        <v>0.9983675479888916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>152663</v>
+        <v>22228</v>
       </c>
       <c r="E6" t="n">
-        <v>210062</v>
+        <v>26800</v>
       </c>
       <c r="F6" t="n">
-        <v>223771</v>
+        <v>25340</v>
       </c>
       <c r="G6" t="n">
-        <v>190724</v>
+        <v>5126</v>
       </c>
       <c r="H6" t="n">
-        <v>104791</v>
+        <v>9542</v>
       </c>
       <c r="I6" t="n">
-        <v>10550</v>
+        <v>752</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>64965</v>
+        <v>6593</v>
       </c>
       <c r="Z6" t="n">
-        <v>53401</v>
+        <v>5350</v>
       </c>
       <c r="AA6" t="n">
-        <v>109414</v>
+        <v>11081</v>
       </c>
       <c r="AB6" t="n">
-        <v>590209</v>
+        <v>59281</v>
       </c>
       <c r="AC6" t="n">
-        <v>69901</v>
+        <v>7022</v>
       </c>
       <c r="AD6" t="n">
-        <v>4810</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
-        <v>49739</v>
+        <v>13326</v>
       </c>
       <c r="E7" t="n">
-        <v>433026</v>
+        <v>89585</v>
       </c>
       <c r="F7" t="n">
-        <v>1042745</v>
+        <v>158388</v>
       </c>
       <c r="G7" t="n">
-        <v>253977</v>
+        <v>32936</v>
       </c>
       <c r="H7" t="n">
-        <v>3088312</v>
+        <v>203858</v>
       </c>
       <c r="I7" t="n">
-        <v>231992</v>
+        <v>13781</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8097</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>297857</v>
+        <v>30099</v>
       </c>
       <c r="AB7" t="n">
-        <v>76141</v>
+        <v>7694</v>
       </c>
       <c r="AC7" t="n">
-        <v>4597208</v>
+        <v>461241</v>
       </c>
       <c r="AD7" t="n">
-        <v>120458</v>
+        <v>12057</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>148</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>2878</v>
+        <v>832</v>
       </c>
       <c r="E8" t="n">
-        <v>42675</v>
+        <v>10170</v>
       </c>
       <c r="F8" t="n">
-        <v>99415</v>
+        <v>24425</v>
       </c>
       <c r="G8" t="n">
-        <v>36949</v>
+        <v>7512</v>
       </c>
       <c r="H8" t="n">
-        <v>600578</v>
+        <v>106441</v>
       </c>
       <c r="I8" t="n">
-        <v>1151970</v>
+        <v>44395</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>280</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>810</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3314</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2660</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>126056</v>
+        <v>12679</v>
       </c>
       <c r="AD8" t="n">
-        <v>1801493</v>
+        <v>180417</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
